--- a/project/warehouse.xlsx
+++ b/project/warehouse.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\А_Гр\QR\project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/poverinov/Documents/GitHub/QR/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC99F87F-467F-4DCC-979B-19F1C8F01566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4283E35-027C-A945-839D-BA717CA5B33E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="21800" windowHeight="12980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>id</t>
   </si>
@@ -88,6 +85,9 @@
   </si>
   <si>
     <t>/static/images/Ax_Б3.jpg</t>
+  </si>
+  <si>
+    <t>ШИБФ</t>
   </si>
 </sst>
 </file>
@@ -405,109 +405,121 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.3984375" customWidth="1"/>
-    <col min="4" max="4" width="13.53125" customWidth="1"/>
-    <col min="5" max="5" width="14.796875" customWidth="1"/>
-    <col min="6" max="6" width="47.796875" customWidth="1"/>
-    <col min="8" max="8" width="37.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" customWidth="1"/>
+    <col min="5" max="5" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="47.83203125" customWidth="1"/>
+    <col min="9" max="9" width="37.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>123</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>123</v>
+      </c>
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>2</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>234</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>234</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>10</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>345</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4">
+        <v>345</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>5</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>2</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>16</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>18</v>
       </c>
     </row>

--- a/project/warehouse.xlsx
+++ b/project/warehouse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/poverinov/Documents/GitHub/QR/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4283E35-027C-A945-839D-BA717CA5B33E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D31E230-D82B-1741-886E-F45DF34549D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="21800" windowHeight="12980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
